--- a/Take-Home_Ex/Take_home_Ex02/Trade_Exp_Imp_by_Services_201525.xlsx
+++ b/Take-Home_Ex/Take_home_Ex02/Trade_Exp_Imp_by_Services_201525.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8AAC42-CAC5-4C66-8144-EE6B30BD052F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB8FDD4-0D55-47C5-913B-B7B85E407966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="450" windowWidth="21420" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="450" windowWidth="22177" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M060251" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Data Series</t>
   </si>
@@ -120,9 +120,6 @@
   </si>
   <si>
     <t xml:space="preserve">      Others</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Imports Of Services</t>
   </si>
 </sst>
 </file>
@@ -540,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="11" width="24" customWidth="1"/>
@@ -1421,811 +1418,6 @@
         <v>577.1</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="4">
-        <v>469181.5</v>
-      </c>
-      <c r="C26" s="4">
-        <v>438107.8</v>
-      </c>
-      <c r="D26" s="5">
-        <v>409062</v>
-      </c>
-      <c r="E26" s="4">
-        <v>332601.09999999998</v>
-      </c>
-      <c r="F26" s="4">
-        <v>290030.5</v>
-      </c>
-      <c r="G26" s="4">
-        <v>285608.40000000002</v>
-      </c>
-      <c r="H26" s="4">
-        <v>274129.59999999998</v>
-      </c>
-      <c r="I26" s="4">
-        <v>251785.8</v>
-      </c>
-      <c r="J26" s="4">
-        <v>219273.5</v>
-      </c>
-      <c r="K26" s="4">
-        <v>222299.6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="4">
-        <v>9865.1</v>
-      </c>
-      <c r="C27" s="4">
-        <v>9794.7000000000007</v>
-      </c>
-      <c r="D27" s="4">
-        <v>11700.4</v>
-      </c>
-      <c r="E27" s="4">
-        <v>10495.5</v>
-      </c>
-      <c r="F27" s="4">
-        <v>9643.1</v>
-      </c>
-      <c r="G27" s="4">
-        <v>8471.2000000000007</v>
-      </c>
-      <c r="H27" s="4">
-        <v>8133.9</v>
-      </c>
-      <c r="I27" s="4">
-        <v>8766.5</v>
-      </c>
-      <c r="J27" s="4">
-        <v>7913.7</v>
-      </c>
-      <c r="K27" s="4">
-        <v>8341.2000000000007</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="5">
-        <v>1891</v>
-      </c>
-      <c r="C28" s="4">
-        <v>1870.6</v>
-      </c>
-      <c r="D28" s="5">
-        <v>1584</v>
-      </c>
-      <c r="E28" s="4">
-        <v>1243.5</v>
-      </c>
-      <c r="F28" s="4">
-        <v>1241.3</v>
-      </c>
-      <c r="G28" s="4">
-        <v>1546.4</v>
-      </c>
-      <c r="H28" s="4">
-        <v>1333.6</v>
-      </c>
-      <c r="I28" s="4">
-        <v>1109.5999999999999</v>
-      </c>
-      <c r="J28" s="4">
-        <v>1207.2</v>
-      </c>
-      <c r="K28" s="4">
-        <v>929.3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="4">
-        <v>162013.4</v>
-      </c>
-      <c r="C29" s="4">
-        <v>149528.1</v>
-      </c>
-      <c r="D29" s="4">
-        <v>154037.5</v>
-      </c>
-      <c r="E29" s="4">
-        <v>118341.3</v>
-      </c>
-      <c r="F29" s="4">
-        <v>97975.4</v>
-      </c>
-      <c r="G29" s="4">
-        <v>87692.9</v>
-      </c>
-      <c r="H29" s="4">
-        <v>86422.8</v>
-      </c>
-      <c r="I29" s="4">
-        <v>70386.8</v>
-      </c>
-      <c r="J29" s="4">
-        <v>60066.9</v>
-      </c>
-      <c r="K29" s="4">
-        <v>65611.600000000006</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" s="4">
-        <v>41790.5</v>
-      </c>
-      <c r="C30" s="4">
-        <v>34762.6</v>
-      </c>
-      <c r="D30" s="4">
-        <v>21532.400000000001</v>
-      </c>
-      <c r="E30" s="4">
-        <v>5897.8</v>
-      </c>
-      <c r="F30" s="4">
-        <v>9711.4</v>
-      </c>
-      <c r="G30" s="4">
-        <v>38098.1</v>
-      </c>
-      <c r="H30" s="4">
-        <v>35738.199999999997</v>
-      </c>
-      <c r="I30" s="4">
-        <v>34308.199999999997</v>
-      </c>
-      <c r="J30" s="4">
-        <v>33063.4</v>
-      </c>
-      <c r="K30" s="4">
-        <v>32524.9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="4">
-        <v>10605.2</v>
-      </c>
-      <c r="C31" s="4">
-        <v>9238.2000000000007</v>
-      </c>
-      <c r="D31" s="4">
-        <v>10755.6</v>
-      </c>
-      <c r="E31" s="4">
-        <v>7856.9</v>
-      </c>
-      <c r="F31" s="4">
-        <v>9124.7999999999993</v>
-      </c>
-      <c r="G31" s="4">
-        <v>7480.9</v>
-      </c>
-      <c r="H31" s="4">
-        <v>6664.8</v>
-      </c>
-      <c r="I31" s="4">
-        <v>5572.4</v>
-      </c>
-      <c r="J31" s="4">
-        <v>6032.9</v>
-      </c>
-      <c r="K31" s="4">
-        <v>4376.7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B32" s="4">
-        <v>383.7</v>
-      </c>
-      <c r="C32" s="4">
-        <v>335.7</v>
-      </c>
-      <c r="D32" s="5">
-        <v>327</v>
-      </c>
-      <c r="E32" s="4">
-        <v>299.89999999999998</v>
-      </c>
-      <c r="F32" s="4">
-        <v>288.89999999999998</v>
-      </c>
-      <c r="G32" s="4">
-        <v>315.60000000000002</v>
-      </c>
-      <c r="H32" s="4">
-        <v>311.10000000000002</v>
-      </c>
-      <c r="I32" s="4">
-        <v>293.39999999999998</v>
-      </c>
-      <c r="J32" s="4">
-        <v>310.3</v>
-      </c>
-      <c r="K32" s="4">
-        <v>274.7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" s="4">
-        <v>1010.4</v>
-      </c>
-      <c r="C33" s="4">
-        <v>900.2</v>
-      </c>
-      <c r="D33" s="4">
-        <v>797.6</v>
-      </c>
-      <c r="E33" s="4">
-        <v>791.9</v>
-      </c>
-      <c r="F33" s="4">
-        <v>678.7</v>
-      </c>
-      <c r="G33" s="4">
-        <v>648.1</v>
-      </c>
-      <c r="H33" s="4">
-        <v>748.8</v>
-      </c>
-      <c r="I33" s="5">
-        <v>519</v>
-      </c>
-      <c r="J33" s="4">
-        <v>514.1</v>
-      </c>
-      <c r="K33" s="4">
-        <v>466.9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" s="4">
-        <v>23225.3</v>
-      </c>
-      <c r="C34" s="4">
-        <v>20671.3</v>
-      </c>
-      <c r="D34" s="4">
-        <v>16641.2</v>
-      </c>
-      <c r="E34" s="4">
-        <v>14914.9</v>
-      </c>
-      <c r="F34" s="4">
-        <v>13777.4</v>
-      </c>
-      <c r="G34" s="4">
-        <v>10250.799999999999</v>
-      </c>
-      <c r="H34" s="4">
-        <v>9140.6</v>
-      </c>
-      <c r="I34" s="4">
-        <v>7848.2</v>
-      </c>
-      <c r="J34" s="4">
-        <v>6458.8</v>
-      </c>
-      <c r="K34" s="5">
-        <v>6194</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B35" s="4">
-        <v>43523.1</v>
-      </c>
-      <c r="C35" s="4">
-        <v>41563.9</v>
-      </c>
-      <c r="D35" s="4">
-        <v>34991.9</v>
-      </c>
-      <c r="E35" s="4">
-        <v>35848.9</v>
-      </c>
-      <c r="F35" s="4">
-        <v>31135.5</v>
-      </c>
-      <c r="G35" s="4">
-        <v>22683.7</v>
-      </c>
-      <c r="H35" s="4">
-        <v>19516.5</v>
-      </c>
-      <c r="I35" s="4">
-        <v>20531.7</v>
-      </c>
-      <c r="J35" s="4">
-        <v>17374.599999999999</v>
-      </c>
-      <c r="K35" s="4">
-        <v>14932.2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B36" s="4">
-        <v>24062.5</v>
-      </c>
-      <c r="C36" s="4">
-        <v>23205.599999999999</v>
-      </c>
-      <c r="D36" s="4">
-        <v>22829.8</v>
-      </c>
-      <c r="E36" s="4">
-        <v>22070.3</v>
-      </c>
-      <c r="F36" s="4">
-        <v>21108.1</v>
-      </c>
-      <c r="G36" s="4">
-        <v>21028.1</v>
-      </c>
-      <c r="H36" s="5">
-        <v>23275</v>
-      </c>
-      <c r="I36" s="4">
-        <v>21809.8</v>
-      </c>
-      <c r="J36" s="4">
-        <v>21622.5</v>
-      </c>
-      <c r="K36" s="5">
-        <v>26672</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B37" s="4">
-        <v>1819.6</v>
-      </c>
-      <c r="C37" s="4">
-        <v>1764.6</v>
-      </c>
-      <c r="D37" s="4">
-        <v>1739.8</v>
-      </c>
-      <c r="E37" s="4">
-        <v>1336.2</v>
-      </c>
-      <c r="F37" s="4">
-        <v>1059.0999999999999</v>
-      </c>
-      <c r="G37" s="4">
-        <v>1058.9000000000001</v>
-      </c>
-      <c r="H37" s="5">
-        <v>926</v>
-      </c>
-      <c r="I37" s="5">
-        <v>599</v>
-      </c>
-      <c r="J37" s="4">
-        <v>542.29999999999995</v>
-      </c>
-      <c r="K37" s="4">
-        <v>685.2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
-      <c r="A38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B38" s="4">
-        <v>148991.70000000001</v>
-      </c>
-      <c r="C38" s="4">
-        <v>144472.29999999999</v>
-      </c>
-      <c r="D38" s="4">
-        <v>132124.79999999999</v>
-      </c>
-      <c r="E38" s="5">
-        <v>113504</v>
-      </c>
-      <c r="F38" s="4">
-        <v>94286.8</v>
-      </c>
-      <c r="G38" s="4">
-        <v>86333.7</v>
-      </c>
-      <c r="H38" s="4">
-        <v>81918.3</v>
-      </c>
-      <c r="I38" s="4">
-        <v>80041.2</v>
-      </c>
-      <c r="J38" s="4">
-        <v>64166.8</v>
-      </c>
-      <c r="K38" s="4">
-        <v>61290.9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B39" s="4">
-        <v>1180.5999999999999</v>
-      </c>
-      <c r="C39" s="4">
-        <v>1154.3</v>
-      </c>
-      <c r="D39" s="4">
-        <v>951.5</v>
-      </c>
-      <c r="E39" s="5">
-        <v>624</v>
-      </c>
-      <c r="F39" s="4">
-        <v>634.1</v>
-      </c>
-      <c r="G39" s="5">
-        <v>556</v>
-      </c>
-      <c r="H39" s="4">
-        <v>486.8</v>
-      </c>
-      <c r="I39" s="4">
-        <v>417.4</v>
-      </c>
-      <c r="J39" s="5">
-        <v>392</v>
-      </c>
-      <c r="K39" s="5">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B40" s="4">
-        <v>30918.1</v>
-      </c>
-      <c r="C40" s="4">
-        <v>29915.599999999999</v>
-      </c>
-      <c r="D40" s="4">
-        <v>24135.3</v>
-      </c>
-      <c r="E40" s="4">
-        <v>20429.3</v>
-      </c>
-      <c r="F40" s="4">
-        <v>15587.3</v>
-      </c>
-      <c r="G40" s="4">
-        <v>13898.5</v>
-      </c>
-      <c r="H40" s="4">
-        <v>10265.5</v>
-      </c>
-      <c r="I40" s="4">
-        <v>8057.1</v>
-      </c>
-      <c r="J40" s="4">
-        <v>4258.7</v>
-      </c>
-      <c r="K40" s="4">
-        <v>3808.8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" s="4">
-        <v>57.8</v>
-      </c>
-      <c r="C41" s="4">
-        <v>56.2</v>
-      </c>
-      <c r="D41" s="4">
-        <v>59.6</v>
-      </c>
-      <c r="E41" s="4">
-        <v>62.4</v>
-      </c>
-      <c r="F41" s="4">
-        <v>57.5</v>
-      </c>
-      <c r="G41" s="4">
-        <v>52.1</v>
-      </c>
-      <c r="H41" s="4">
-        <v>66.8</v>
-      </c>
-      <c r="I41" s="4">
-        <v>56.1</v>
-      </c>
-      <c r="J41" s="5">
-        <v>72</v>
-      </c>
-      <c r="K41" s="4">
-        <v>46.9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="A42" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B42" s="4">
-        <v>50386.2</v>
-      </c>
-      <c r="C42" s="4">
-        <v>49473.8</v>
-      </c>
-      <c r="D42" s="4">
-        <v>42834.9</v>
-      </c>
-      <c r="E42" s="4">
-        <v>36476.5</v>
-      </c>
-      <c r="F42" s="4">
-        <v>31711.599999999999</v>
-      </c>
-      <c r="G42" s="5">
-        <v>30668</v>
-      </c>
-      <c r="H42" s="4">
-        <v>26665.1</v>
-      </c>
-      <c r="I42" s="4">
-        <v>24180.799999999999</v>
-      </c>
-      <c r="J42" s="4">
-        <v>21891.3</v>
-      </c>
-      <c r="K42" s="4">
-        <v>18749.900000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B43" s="5">
-        <v>7910</v>
-      </c>
-      <c r="C43" s="4">
-        <v>7639.7</v>
-      </c>
-      <c r="D43" s="4">
-        <v>6954.3</v>
-      </c>
-      <c r="E43" s="4">
-        <v>6057.4</v>
-      </c>
-      <c r="F43" s="4">
-        <v>5187.6000000000004</v>
-      </c>
-      <c r="G43" s="4">
-        <v>4438.6000000000004</v>
-      </c>
-      <c r="H43" s="4">
-        <v>3347.7</v>
-      </c>
-      <c r="I43" s="4">
-        <v>3208.7</v>
-      </c>
-      <c r="J43" s="4">
-        <v>3323.7</v>
-      </c>
-      <c r="K43" s="4">
-        <v>3286.9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B44" s="4">
-        <v>1009.5</v>
-      </c>
-      <c r="C44" s="4">
-        <v>983.7</v>
-      </c>
-      <c r="D44" s="4">
-        <v>725.6</v>
-      </c>
-      <c r="E44" s="4">
-        <v>719.2</v>
-      </c>
-      <c r="F44" s="4">
-        <v>607.1</v>
-      </c>
-      <c r="G44" s="4">
-        <v>456.4</v>
-      </c>
-      <c r="H44" s="5">
-        <v>415</v>
-      </c>
-      <c r="I44" s="4">
-        <v>360.6</v>
-      </c>
-      <c r="J44" s="4">
-        <v>336.7</v>
-      </c>
-      <c r="K44" s="4">
-        <v>315.39999999999998</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B45" s="4">
-        <v>30345.1</v>
-      </c>
-      <c r="C45" s="4">
-        <v>29120.3</v>
-      </c>
-      <c r="D45" s="4">
-        <v>27632.1</v>
-      </c>
-      <c r="E45" s="4">
-        <v>25657.8</v>
-      </c>
-      <c r="F45" s="4">
-        <v>21688.400000000001</v>
-      </c>
-      <c r="G45" s="4">
-        <v>18227.099999999999</v>
-      </c>
-      <c r="H45" s="5">
-        <v>19070</v>
-      </c>
-      <c r="I45" s="4">
-        <v>22423.8</v>
-      </c>
-      <c r="J45" s="4">
-        <v>14547.3</v>
-      </c>
-      <c r="K45" s="4">
-        <v>17126.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
-      <c r="A46" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B46" s="4">
-        <v>7291.2</v>
-      </c>
-      <c r="C46" s="4">
-        <v>7091.1</v>
-      </c>
-      <c r="D46" s="4">
-        <v>8417.1</v>
-      </c>
-      <c r="E46" s="4">
-        <v>4983.7</v>
-      </c>
-      <c r="F46" s="5">
-        <v>3736</v>
-      </c>
-      <c r="G46" s="4">
-        <v>4701.3999999999996</v>
-      </c>
-      <c r="H46" s="4">
-        <v>5396.8</v>
-      </c>
-      <c r="I46" s="4">
-        <v>5549.6</v>
-      </c>
-      <c r="J46" s="4">
-        <v>4843.3</v>
-      </c>
-      <c r="K46" s="4">
-        <v>5177.3999999999996</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
-      <c r="A47" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B47" s="4">
-        <v>19117.599999999999</v>
-      </c>
-      <c r="C47" s="4">
-        <v>18268.5</v>
-      </c>
-      <c r="D47" s="4">
-        <v>19779.900000000001</v>
-      </c>
-      <c r="E47" s="5">
-        <v>17951</v>
-      </c>
-      <c r="F47" s="4">
-        <v>14728.9</v>
-      </c>
-      <c r="G47" s="4">
-        <v>12960.6</v>
-      </c>
-      <c r="H47" s="4">
-        <v>15837.2</v>
-      </c>
-      <c r="I47" s="4">
-        <v>15394.7</v>
-      </c>
-      <c r="J47" s="4">
-        <v>14106.6</v>
-      </c>
-      <c r="K47" s="5">
-        <v>12097</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
-      <c r="A48" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B48" s="4">
-        <v>775.6</v>
-      </c>
-      <c r="C48" s="4">
-        <v>769.1</v>
-      </c>
-      <c r="D48" s="4">
-        <v>634.5</v>
-      </c>
-      <c r="E48" s="4">
-        <v>542.70000000000005</v>
-      </c>
-      <c r="F48" s="4">
-        <v>348.3</v>
-      </c>
-      <c r="G48" s="5">
-        <v>375</v>
-      </c>
-      <c r="H48" s="4">
-        <v>367.4</v>
-      </c>
-      <c r="I48" s="4">
-        <v>392.4</v>
-      </c>
-      <c r="J48" s="4">
-        <v>395.2</v>
-      </c>
-      <c r="K48" s="4">
-        <v>351.1</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
